--- a/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27431" windowHeight="13068" activeTab="1"/>
+    <workbookView windowWidth="20184" windowHeight="13068" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="319">
   <si>
     <t>核心风格关键词： Synthwave, Retrowave, Neon Arcade, Dark Grid Background, Vector Flat, Glowing.</t>
   </si>
@@ -380,6 +380,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>废土装甲</t>
     </r>
     <r>
@@ -560,80 +567,55 @@
     <t>Splitter (分裂岩浆)</t>
   </si>
   <si>
-    <t>中大圆形，边缘起伏冒泡</t>
-  </si>
-  <si>
-    <t>三对惊恐小眼，挤在一起</t>
-  </si>
-  <si>
-    <t>身体表面覆盖 3个亮黄色发光圆核</t>
-  </si>
-  <si>
-    <t>冒泡、融合、超载</t>
+    <t>三角形或3个圆形</t>
+  </si>
+  <si>
+    <t>三只惊恐黄色眼睛</t>
+  </si>
+  <si>
+    <t>身上部分覆盖着深色、锯齿状的冷却黑曜石岩石盔甲作为装饰。</t>
+  </si>
+  <si>
+    <t>分裂、惊恐</t>
   </si>
   <si>
     <t>像过载细胞一样包裹着多个核心的流体。</t>
   </si>
   <si>
+    <t>分裂的小岩浆粘液怪</t>
+  </si>
+  <si>
     <t>Exploder (自爆爆裂者)</t>
   </si>
   <si>
-    <t>极度膨胀的正圆形。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>瞪大的狂躁眼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>紧密拼接的橙色几何碎片装甲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <t>白炽、膨胀、危险</t>
+    <t>圆形炸弹形状</t>
+  </si>
+  <si>
+    <t>一双充满红血丝的、极其狂躁的黄色大眼睛</t>
+  </si>
+  <si>
+    <t>头顶喷发着一簇像炸弹引线一样燃烧的明亮火焰。身体被一层薄薄的、深色的冷却火山岩皮包裹着，岩皮上布满了巨大的裂纹，刺眼的炽热熔岩从裂纹中闪耀而出。</t>
+  </si>
+  <si>
+    <t>膨胀、危险</t>
   </si>
   <si>
     <t>完美圆润的膨胀流体，濒临自爆的炸弹</t>
   </si>
   <si>
-    <t>Artillery (熔岩喷吐)</t>
+    <t>自爆留下的一滩岩浆</t>
+  </si>
+  <si>
+    <t>熔岩坦克</t>
+  </si>
+  <si>
+    <t>半眯蔑视眼</t>
+  </si>
+  <si>
+    <t>身体表面超过 80% 被极其巨大、厚重的黑曜石岩石装甲板拼接覆盖。</t>
+  </si>
+  <si>
+    <t>Artillery (熔岩炮手)</t>
   </si>
   <si>
     <t>底部宽大的圆锥形/水滴形</t>
@@ -732,25 +714,25 @@
     <t>巨大的球体，表面附着冷却的黑曜石装甲碎片</t>
   </si>
   <si>
-    <t>Abyssal Furnace（深渊巨炉 BOSS）</t>
-  </si>
-  <si>
-    <t>极其巨大的环形/甜甜圈形</t>
-  </si>
-  <si>
-    <t>没有独眼。透过栅栏的缝隙，能看到深渊底部传来极其刺眼的白热化脉冲光</t>
-  </si>
-  <si>
-    <t>环形的中间空洞处，被一个极其沉重、粗壮的黑曜石十字铸铁栅栏死死锁住。岩浆流体在环形四周沸腾。</t>
-  </si>
-  <si>
-    <t>一座活体火山口、一个失控的熔炉</t>
-  </si>
-  <si>
-    <t>Frost Tank (冰甲巨兽)</t>
-  </si>
-  <si>
-    <t>庞大正圆形</t>
+    <t>熔岩BOSS</t>
+  </si>
+  <si>
+    <t>巨大的圆锥形火山</t>
+  </si>
+  <si>
+    <t>一双令人恐惧的恶魔眼睛，发出纯黄色的光芒。</t>
+  </si>
+  <si>
+    <t>主体部分覆盖着极其厚实、锯齿状、深灰色的玄武岩脊状物。在前方/顶部有一个巨大的火山口，喷出炽热的熔岩。</t>
+  </si>
+  <si>
+    <t>一座活体火山</t>
+  </si>
+  <si>
+    <t>冰霜粘液怪</t>
+  </si>
+  <si>
+    <t>Frost Tank (冰甲卫士)</t>
   </si>
   <si>
     <t>冷酷无情的幽蓝小瞳孔</t>
@@ -768,30 +750,7 @@
     <t>Aura (极寒光环)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>完美的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>正六边形</t>
-    </r>
-  </si>
-  <si>
-    <t>闭目祈祷眼 (带长睫毛)</t>
+    <t>冷漠的半闭眼（高傲感），冰蓝色眼珠</t>
   </si>
   <si>
     <t>正中心发光六角冰晶 + 底部冰雪法阵</t>
@@ -806,7 +765,7 @@
     <t>Frostcaster (霜冻施法)</t>
   </si>
   <si>
-    <t>瘦长的高挑圆柱形/竖椭圆</t>
+    <t>瘦长的高挑圆柱形/竖椭圆 水滴形</t>
   </si>
   <si>
     <t>锐利散发魔力的倒三角眼</t>
@@ -1915,7 +1874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1977,6 +1936,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2022,13 +1984,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2355,7 +2326,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="103" customHeight="1" spans="1:4">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2643,7 +2614,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="35.3333333333333" style="1" customWidth="1"/>
@@ -2732,10 +2703,10 @@
       </c>
     </row>
     <row r="8" ht="28.95" customHeight="1" spans="1:3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>79</v>
       </c>
       <c r="C8" s="16"/>
@@ -2744,7 +2715,7 @@
       <c r="A9" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -2755,7 +2726,7 @@
       <c r="A10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>84</v>
       </c>
       <c r="C10" s="16" t="s">
@@ -2766,7 +2737,7 @@
       <c r="A11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="16"/>
@@ -2802,39 +2773,39 @@
     </row>
     <row r="20" ht="15.15" customHeight="1"/>
     <row r="21" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="26" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="22" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="30" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="19" t="s">
@@ -2842,19 +2813,19 @@
       </c>
     </row>
     <row r="23" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="30" t="s">
         <v>111</v>
       </c>
       <c r="F23" s="19" t="s">
@@ -2862,19 +2833,19 @@
       </c>
     </row>
     <row r="24" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="30" t="s">
         <v>117</v>
       </c>
       <c r="F24" s="19" t="s">
@@ -2882,19 +2853,19 @@
       </c>
     </row>
     <row r="25" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="28" t="s">
         <v>123</v>
       </c>
       <c r="F25" s="19" t="s">
@@ -2902,39 +2873,39 @@
       </c>
     </row>
     <row r="26" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="34" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="27" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="30" t="s">
         <v>135</v>
       </c>
       <c r="F27" s="19" t="s">
@@ -2942,19 +2913,19 @@
       </c>
     </row>
     <row r="28" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="36" t="s">
         <v>139</v>
       </c>
       <c r="F28" s="19" t="s">
@@ -2962,372 +2933,440 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="36" t="s">
         <v>143</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" ht="28.8" spans="1:6">
       <c r="A30" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="37" t="s">
         <v>148</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="36" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="19" t="s">
+    <row r="31" s="21" customFormat="1" spans="1:6">
+      <c r="A31" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" s="21" customFormat="1" ht="43.2" spans="1:6">
+      <c r="A32" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="B32" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="C32" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="D32" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="E32" s="20" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="19" t="s">
+      <c r="F32" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="35" t="s">
+    </row>
+    <row r="33" s="21" customFormat="1" spans="1:6">
+      <c r="A33" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="B33" s="39"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="37"/>
+    </row>
+    <row r="34" s="21" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A34" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="B34" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="E32" s="35" t="s">
+      <c r="D34" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="F32" s="35" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" s="21" customFormat="1" spans="1:6">
-      <c r="A33" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F33" s="37"/>
-    </row>
-    <row r="34" customFormat="1" spans="1:6">
-      <c r="A34" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="E34" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="F34" s="35"/>
+      <c r="E34" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="37"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" s="22" customFormat="1" spans="1:6">
+      <c r="A36" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" s="40"/>
+    </row>
+    <row r="37" s="22" customFormat="1" spans="1:6">
+      <c r="A37" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B37" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C37" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D37" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E37" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F37" s="40"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="19" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="19" t="s">
+      <c r="B38" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="C38" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="D38" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="E38" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="F38" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="F36" s="35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" s="21" customFormat="1" spans="1:6">
-      <c r="A37" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="B37" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="C37" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A38" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="F38" s="35"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" s="22" customFormat="1" spans="1:6">
+      <c r="A40" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A41" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B41" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C41" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D41" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E41" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="F41" s="36"/>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
+      <c r="A42" s="19" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="19" t="s">
+      <c r="B42" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B43" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="D43" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="E43" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="F43" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B41" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" s="21" customFormat="1" spans="1:6">
-      <c r="A42" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="B42" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A43" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" t="s">
-        <v>223</v>
-      </c>
-      <c r="F43" s="35"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" s="35" t="s">
-        <v>227</v>
+        <v>206</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>208</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>229</v>
+        <v>209</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" s="22" customFormat="1" spans="1:6">
+      <c r="A46" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" s="22" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A47" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="40"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="D48" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="E48" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="F48" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="E45" s="19" t="s">
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="B49" s="36" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="46" s="21" customFormat="1" spans="1:6">
-      <c r="A46" s="33" t="s">
+      <c r="C49" s="36" t="s">
         <v>236</v>
       </c>
-      <c r="B46" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="C46" s="33" t="s">
+      <c r="D49" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="E49" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="E46" s="33" t="s">
+      <c r="F49" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="F46" s="37" t="s">
+    </row>
+    <row r="50" s="22" customFormat="1" spans="1:6">
+      <c r="A50" s="34" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="47" ht="28.8" spans="1:6">
-      <c r="A47" s="35" t="s">
+      <c r="B50" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C50" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="D50" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="38" t="s">
+      <c r="E50" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="F50" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="E47" s="38" t="s">
+    </row>
+    <row r="51" ht="28.8" spans="1:6">
+      <c r="A51" s="36" t="s">
         <v>245</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3358,125 +3397,125 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" ht="15.15" customHeight="1" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="15.15" customHeight="1" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" ht="15.15" customHeight="1" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" ht="15.15" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" ht="15.15" customHeight="1" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" ht="15.15" customHeight="1" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="12" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -3497,30 +3536,30 @@
     </row>
     <row r="21" ht="43.95" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" ht="29.55" customHeight="1" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" ht="15.15" customHeight="1"/>
@@ -3540,110 +3579,110 @@
     </row>
     <row r="29" ht="58.35" customHeight="1" spans="1:5">
       <c r="A29" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" ht="43.95" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E30" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" ht="58.35" customHeight="1" spans="1:5">
       <c r="A31" s="8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E31" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" ht="43.95" customHeight="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" ht="29.55" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" ht="43.2" customHeight="1" spans="1:4">
       <c r="A34" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" ht="87" customHeight="1" spans="1:4">
       <c r="A35" s="19"/>
       <c r="B35" s="19" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D35" s="19"/>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20184" windowHeight="13068" activeTab="1"/>
+    <workbookView windowWidth="19871" windowHeight="13068" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="317">
   <si>
     <t>核心风格关键词： Synthwave, Retrowave, Neon Arcade, Dark Grid Background, Vector Flat, Glowing.</t>
   </si>
@@ -334,7 +334,29 @@
     <t>描述 (Description)</t>
   </si>
   <si>
-    <t>Slime (粘液)</t>
+    <r>
+      <t>Dark_Slime (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>粘液</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>正圆形</t>
@@ -370,7 +392,29 @@
     <t>速度极快，像子弹一样冲过来的带刺液滴</t>
   </si>
   <si>
-    <t>Tank (硬壳)</t>
+    <r>
+      <t>Tank (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深暗重甲</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>圆角方块</t>
@@ -582,7 +626,7 @@
     <t>像过载细胞一样包裹着多个核心的流体。</t>
   </si>
   <si>
-    <t>分裂的小岩浆粘液怪</t>
+    <t>Lava_Slime(分裂的小岩浆粘液怪)</t>
   </si>
   <si>
     <t>Exploder (自爆爆裂者)</t>
@@ -591,117 +635,136 @@
     <t>圆形炸弹形状</t>
   </si>
   <si>
+    <t>表面贴附带龟裂纹路的深色结壳装甲</t>
+  </si>
+  <si>
+    <t>膨胀、危险</t>
+  </si>
+  <si>
+    <t>完美圆润的膨胀流体，濒临自爆的炸弹</t>
+  </si>
+  <si>
+    <t>自爆留下的一滩岩浆</t>
+  </si>
+  <si>
+    <t>头顶喷发着一簇像炸弹引线一样燃烧的明亮火焰。身体被一层薄薄的、深色的冷却火山岩皮包裹着，岩皮上布满了巨大的裂纹，刺眼的炽热熔岩从裂纹中闪耀而出。</t>
+  </si>
+  <si>
+    <r>
+      <t>Tank (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>熔岩重甲</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>半眯蔑视眼</t>
+  </si>
+  <si>
+    <t>身体表面超过 80% 被极其巨大、厚重的黑曜石岩石装甲板拼接覆盖。</t>
+  </si>
+  <si>
+    <t>Artillery (熔岩炮手)</t>
+  </si>
+  <si>
+    <t>底部宽大的圆锥形/水滴形</t>
+  </si>
+  <si>
+    <t>愤怒眼</t>
+  </si>
+  <si>
+    <t>顶部镶嵌高亮岩浆喷发口</t>
+  </si>
+  <si>
+    <t>稳重、蓄力、炮台</t>
+  </si>
+  <si>
+    <t>底部宽大顶部收缩，像一座移动的微型活火山口</t>
+  </si>
+  <si>
+    <t>Ash Glider（灰烬滑翔者）</t>
+  </si>
+  <si>
+    <t>横向宽扁的菱形</t>
+  </si>
+  <si>
+    <t>晕眩眼/蚊香眼</t>
+  </si>
+  <si>
+    <t>身体两侧带有向上扬起的亮橙色火焰状滑翔鳍</t>
+  </si>
+  <si>
+    <t>轻盈、漂移、火痕</t>
+  </si>
+  <si>
+    <t>Magma Roller（熔岩滚轮）</t>
+  </si>
+  <si>
+    <t>宽扁的胶囊形 / 药丸形</t>
+  </si>
+  <si>
+    <t>晕眩的蚊香眼</t>
+  </si>
+  <si>
+    <t>身体正中央环绕着一圈带有粗糙尖刺的黑曜石履带装甲</t>
+  </si>
+  <si>
+    <t>沉重、碾压、车轮。</t>
+  </si>
+  <si>
+    <t>Elite Exploder (精英核爆)</t>
+  </si>
+  <si>
     <t>一双充满红血丝的、极其狂躁的黄色大眼睛</t>
   </si>
   <si>
-    <t>头顶喷发着一簇像炸弹引线一样燃烧的明亮火焰。身体被一层薄薄的、深色的冷却火山岩皮包裹着，岩皮上布满了巨大的裂纹，刺眼的炽热熔岩从裂纹中闪耀而出。</t>
-  </si>
-  <si>
-    <t>膨胀、危险</t>
-  </si>
-  <si>
-    <t>完美圆润的膨胀流体，濒临自爆的炸弹</t>
-  </si>
-  <si>
-    <t>自爆留下的一滩岩浆</t>
-  </si>
-  <si>
-    <t>熔岩坦克</t>
-  </si>
-  <si>
-    <t>半眯蔑视眼</t>
-  </si>
-  <si>
-    <t>身体表面超过 80% 被极其巨大、厚重的黑曜石岩石装甲板拼接覆盖。</t>
-  </si>
-  <si>
-    <t>Artillery (熔岩炮手)</t>
-  </si>
-  <si>
-    <t>底部宽大的圆锥形/水滴形</t>
-  </si>
-  <si>
-    <t>专注狙击手眼 (位于底部)</t>
-  </si>
-  <si>
-    <t>顶部镶嵌高亮岩浆喷发口</t>
-  </si>
-  <si>
-    <t>稳重、蓄力、炮台</t>
-  </si>
-  <si>
-    <t>底部宽大顶部收缩，像一座移动的微型活火山口</t>
-  </si>
-  <si>
-    <t>Ash Glider（灰烬滑翔者）</t>
-  </si>
-  <si>
-    <t>横向宽扁的菱形</t>
-  </si>
-  <si>
-    <t>晕眩眼/蚊香眼</t>
-  </si>
-  <si>
-    <t>身体两侧带有向上扬起的亮橙色火焰状滑翔鳍</t>
-  </si>
-  <si>
-    <t>轻盈、漂移、火痕</t>
-  </si>
-  <si>
-    <t>Magma Roller（熔岩滚轮）</t>
-  </si>
-  <si>
-    <t>宽扁的胶囊形 / 药丸形</t>
-  </si>
-  <si>
-    <t>晕眩的蚊香眼</t>
-  </si>
-  <si>
-    <t>身体正中央环绕着一圈带有粗糙尖刺的黑曜石履带装甲</t>
-  </si>
-  <si>
-    <t>沉重、碾压、车轮。</t>
-  </si>
-  <si>
-    <t>Elite Exploder (精英核爆)</t>
+    <t>极度膨胀、过热</t>
+  </si>
+  <si>
+    <t>自爆爆裂者的放大版，濒临撑破的巨型过热流体。</t>
+  </si>
+  <si>
+    <t>Elite Splitter (精英巨型分裂)</t>
+  </si>
+  <si>
+    <t>7角星</t>
+  </si>
+  <si>
+    <t>7只惊恐黄色眼睛</t>
+  </si>
+  <si>
+    <t>身体表面覆盖着 7个 独立的黄色眼睛，边缘有熔岩石块覆盖</t>
+  </si>
+  <si>
+    <t>诡异融合、母体</t>
+  </si>
+  <si>
+    <t>分裂岩浆怪的放大版，像一滩流动的岩浆沼泽母体。</t>
+  </si>
+  <si>
+    <t>Magma Core (熔岩之核 BOSS)</t>
   </si>
   <si>
     <t>巨大正圆形</t>
   </si>
   <si>
-    <t>高温扭曲的亮痕 (无瞳孔)</t>
-  </si>
-  <si>
-    <t>表面贴附带龟裂纹路的深色结壳装甲，环绕剧烈火星</t>
-  </si>
-  <si>
-    <t>极度膨胀、过热</t>
-  </si>
-  <si>
-    <t>自爆爆裂者的放大版，濒临撑破的巨型过热流体。</t>
-  </si>
-  <si>
-    <t>Elite Splitter (精英巨型分裂)</t>
-  </si>
-  <si>
-    <t>宽大、不规则的扁平椭圆</t>
-  </si>
-  <si>
-    <t>多对大小不一的慵懒半眯眼</t>
-  </si>
-  <si>
-    <t>身体表面覆盖着 5-6个 独立的亮黄色岩浆核心</t>
-  </si>
-  <si>
-    <t>诡异融合、母体</t>
-  </si>
-  <si>
-    <t>分裂岩浆怪的放大版，像一滩流动的岩浆沼泽母体。</t>
-  </si>
-  <si>
-    <t>Magma Core (熔岩之核 BOSS)</t>
-  </si>
-  <si>
     <t>正中心一道刺眼的十字形发光裂缝</t>
   </si>
   <si>
@@ -732,10 +795,10 @@
     <t>冰霜粘液怪</t>
   </si>
   <si>
-    <t>Frost Tank (冰甲卫士)</t>
-  </si>
-  <si>
-    <t>冷酷无情的幽蓝小瞳孔</t>
+    <t>头顶有冰晶</t>
+  </si>
+  <si>
+    <t>Tank (极寒重甲)</t>
   </si>
   <si>
     <t>外部包裹几块半透明的多边形几何冰晶装甲</t>
@@ -750,25 +813,22 @@
     <t>Aura (极寒光环)</t>
   </si>
   <si>
-    <t>冷漠的半闭眼（高傲感），冰蓝色眼珠</t>
-  </si>
-  <si>
-    <t>正中心发光六角冰晶 + 底部冰雪法阵</t>
+    <t>头顶冰晶王冠</t>
   </si>
   <si>
     <t>轻盈、圣洁、致命</t>
   </si>
   <si>
-    <t>一朵悬浮的精致雪花，底盘带有华丽的冰雪减伤法阵</t>
-  </si>
-  <si>
-    <t>Frostcaster (霜冻施法)</t>
+    <t>自爆加速怪物和怪物增伤</t>
+  </si>
+  <si>
+    <t>Caster (霜冻施法)</t>
   </si>
   <si>
     <t>瘦长的高挑圆柱形/竖椭圆 水滴形</t>
   </si>
   <si>
-    <t>锐利散发魔力的倒三角眼</t>
+    <t>狡黠/阴险眼</t>
   </si>
   <si>
     <t>头顶正上方悬浮散发寒气的完美冰球</t>
@@ -833,7 +893,7 @@
     <t>平滑、反光、坚不可摧</t>
   </si>
   <si>
-    <t>Elite Shield Guard (精英绝对屏障)</t>
+    <t>Elite Shield Guard (精英-冰甲卫士)</t>
   </si>
   <si>
     <t>厚实半圆形</t>
@@ -1176,7 +1236,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1217,6 +1277,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1744,137 +1811,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1987,16 +2054,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2326,7 +2396,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="103" customHeight="1" spans="1:4">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2620,7 +2690,7 @@
     <col min="1" max="1" width="35.3333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="34.7777777777778" style="1" customWidth="1"/>
     <col min="3" max="3" width="35.4444444444444" style="1" customWidth="1"/>
-    <col min="4" max="4" width="52.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="61.3333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.5555555555556" style="1" customWidth="1"/>
     <col min="6" max="6" width="60.7777777777778" customWidth="1"/>
   </cols>
@@ -2992,38 +3062,40 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" s="21" customFormat="1" ht="43.2" spans="1:6">
+    <row r="32" s="21" customFormat="1" spans="1:6">
       <c r="A32" s="20" t="s">
         <v>152</v>
       </c>
       <c r="B32" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="E32" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="F32" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="F32" s="37" t="s">
+    </row>
+    <row r="33" s="21" customFormat="1" ht="43.2" spans="1:6">
+      <c r="A33" s="20" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="33" s="21" customFormat="1" spans="1:6">
-      <c r="A33" s="20" t="s">
+      <c r="B33" s="38"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
       <c r="E33" s="30"/>
       <c r="F33" s="37"/>
     </row>
     <row r="34" s="21" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="27" t="s">
         <v>159</v>
       </c>
       <c r="B34" s="28" t="s">
@@ -3096,87 +3168,87 @@
       </c>
       <c r="F37" s="40"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" ht="43.2" spans="1:6">
       <c r="A38" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B38" s="36" t="s">
+      <c r="B38" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="D38" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="F38" s="36" t="s">
         <v>181</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="D39" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="E39" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="F39" s="36" t="s">
         <v>187</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="40" s="22" customFormat="1" spans="1:6">
       <c r="A40" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C40" s="40" t="s">
+      <c r="D40" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="E40" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="F40" s="40" t="s">
         <v>193</v>
-      </c>
-      <c r="F40" s="40" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="41" customFormat="1" ht="28.8" spans="1:6">
       <c r="A41" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="C41" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="D41" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="E41" s="21" t="s">
         <v>198</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>199</v>
       </c>
       <c r="F41" s="36"/>
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" s="28" t="s">
         <v>102</v>
@@ -3184,8 +3256,8 @@
       <c r="C42" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="30" t="s">
-        <v>104</v>
+      <c r="D42" s="28" t="s">
+        <v>200</v>
       </c>
       <c r="E42" s="30" t="s">
         <v>105</v>
@@ -3201,172 +3273,172 @@
       <c r="B43" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="E43" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="F43" s="36" t="s">
         <v>204</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B44" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="F44" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="19" t="s">
+    </row>
+    <row r="45" ht="17.4" spans="1:6">
+      <c r="A45" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="B45" s="36" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="19" t="s">
+      <c r="C45" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="D45" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="E45" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="F45" s="19" t="s">
         <v>214</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="46" s="22" customFormat="1" spans="1:6">
       <c r="A46" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="C46" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="D46" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="E46" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="D46" s="40" t="s">
+      <c r="F46" s="40" t="s">
         <v>220</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="47" s="22" customFormat="1" ht="28.8" spans="1:6">
       <c r="A47" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="40" t="s">
+      <c r="D47" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="E47" s="22" t="s">
         <v>225</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>227</v>
       </c>
       <c r="F47" s="40"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="36" t="s">
+      <c r="D48" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="E48" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="F48" s="36" t="s">
         <v>231</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="D49" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="E49" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="F49" s="36" t="s">
         <v>237</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="50" s="22" customFormat="1" spans="1:6">
       <c r="A50" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="B50" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" s="34" t="s">
+      <c r="E50" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="F50" s="40" t="s">
         <v>242</v>
-      </c>
-      <c r="E50" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="F50" s="40" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="51" ht="28.8" spans="1:6">
       <c r="A51" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="D51" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="E51" s="21" t="s">
         <v>247</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3397,125 +3469,125 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="4" ht="15.15" customHeight="1" spans="1:3">
       <c r="A4" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A5" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" ht="15.15" customHeight="1" spans="1:3">
       <c r="A6" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="8" ht="15.15" customHeight="1" spans="1:3">
       <c r="A8" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="9" ht="15.15" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="10" ht="15.15" customHeight="1" spans="1:3">
       <c r="A10" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>275</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="11" ht="15.15" customHeight="1" spans="1:3">
       <c r="A11" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -3536,30 +3608,30 @@
     </row>
     <row r="21" ht="43.95" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="22" ht="29.55" customHeight="1" spans="1:5">
       <c r="A22" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="27" ht="15.15" customHeight="1"/>
@@ -3579,110 +3651,110 @@
     </row>
     <row r="29" ht="58.35" customHeight="1" spans="1:5">
       <c r="A29" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="D29" s="15" t="s">
         <v>292</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="30" ht="43.95" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" t="s">
         <v>297</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="E30" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="31" ht="58.35" customHeight="1" spans="1:5">
       <c r="A31" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="E31" t="s">
         <v>302</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="E31" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="32" ht="43.95" customHeight="1" spans="1:5">
       <c r="A32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="E32" t="s">
         <v>307</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="E32" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="33" ht="29.55" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="34" ht="43.2" customHeight="1" spans="1:4">
       <c r="A34" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="D34" s="18" t="s">
         <v>314</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="35" ht="87" customHeight="1" spans="1:4">
       <c r="A35" s="19"/>
       <c r="B35" s="19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D35" s="19"/>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19871" windowHeight="13068" activeTab="1"/>
+    <workbookView windowWidth="25163" windowHeight="13068" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -335,6 +335,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Dark_Slime (</t>
     </r>
     <r>
@@ -393,6 +400,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Tank (</t>
     </r>
     <r>
@@ -651,6 +665,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Tank (</t>
     </r>
     <r>
@@ -1941,7 +1962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2050,9 +2071,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -2396,7 +2414,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="103" customHeight="1" spans="1:4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3022,7 +3040,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="30" ht="28.8" spans="1:6">
+    <row r="30" spans="1:6">
       <c r="A30" s="19" t="s">
         <v>145</v>
       </c>
@@ -3032,7 +3050,7 @@
       <c r="C30" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="21" t="s">
         <v>148</v>
       </c>
       <c r="E30" s="19" t="s">
@@ -3066,7 +3084,7 @@
       <c r="A32" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="21" t="s">
         <v>153</v>
       </c>
       <c r="C32" s="29" t="s">
@@ -3078,7 +3096,7 @@
       <c r="E32" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="21" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3086,13 +3104,12 @@
       <c r="A33" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="39" t="s">
+      <c r="B33" s="37"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="38" t="s">
         <v>158</v>
       </c>
       <c r="E33" s="30"/>
-      <c r="F33" s="37"/>
     </row>
     <row r="34" s="21" customFormat="1" ht="28.8" spans="1:6">
       <c r="A34" s="27" t="s">
@@ -3101,16 +3118,15 @@
       <c r="B34" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E34" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="37"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="19" t="s">
@@ -3136,49 +3152,49 @@
       <c r="A36" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="E36" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="40"/>
+      <c r="F36" s="39"/>
     </row>
     <row r="37" s="22" customFormat="1" spans="1:6">
       <c r="A37" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="F37" s="40"/>
+      <c r="F37" s="39"/>
     </row>
     <row r="38" ht="43.2" spans="1:6">
       <c r="A38" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="38" t="s">
         <v>158</v>
       </c>
       <c r="E38" s="19" t="s">
@@ -3212,19 +3228,19 @@
       <c r="A40" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="39" t="s">
         <v>191</v>
       </c>
       <c r="E40" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="F40" s="40" t="s">
+      <c r="F40" s="39" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3290,7 +3306,7 @@
       <c r="A44" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="40" t="s">
         <v>120</v>
       </c>
       <c r="C44" s="29" t="s">
@@ -3313,7 +3329,7 @@
       <c r="B45" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="41" t="s">
         <v>211</v>
       </c>
       <c r="D45" s="36" t="s">
@@ -3330,19 +3346,19 @@
       <c r="A46" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E46" s="40" t="s">
+      <c r="E46" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="F46" s="40" t="s">
+      <c r="F46" s="39" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3350,19 +3366,19 @@
       <c r="A47" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="40" t="s">
+      <c r="B47" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="C47" s="43" t="s">
+      <c r="C47" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="40" t="s">
+      <c r="D47" s="39" t="s">
         <v>224</v>
       </c>
       <c r="E47" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="F47" s="40"/>
+      <c r="F47" s="39"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="19" t="s">
@@ -3408,19 +3424,19 @@
       <c r="A50" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="B50" s="40" t="s">
+      <c r="B50" s="39" t="s">
         <v>189</v>
       </c>
       <c r="C50" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="D50" s="39" t="s">
         <v>240</v>
       </c>
       <c r="E50" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="F50" s="40" t="s">
+      <c r="F50" s="39" t="s">
         <v>242</v>
       </c>
     </row>

--- a/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/美术资产清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25163" windowHeight="13068" activeTab="2"/>
+    <workbookView windowWidth="19500" windowHeight="11231" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="315">
   <si>
     <t>核心风格关键词： Synthwave, Retrowave, Neon Arcade, Dark Grid Background, Vector Flat, Glowing.</t>
   </si>
@@ -846,7 +846,7 @@
     <t>Caster (霜冻施法)</t>
   </si>
   <si>
-    <t>瘦长的高挑圆柱形/竖椭圆 水滴形</t>
+    <t>瘦长的高挑 水滴形</t>
   </si>
   <si>
     <t>狡黠/阴险眼</t>
@@ -861,7 +861,7 @@
     <t>细长液柱，头顶悬浮冰球，蓄力发射冰冻射线</t>
   </si>
   <si>
-    <t>Ice Dart（冰锥突击者）</t>
+    <t>Ice Dart（冰刺炮手）</t>
   </si>
   <si>
     <t>锐利的倒三角形</t>
@@ -917,9 +917,6 @@
     <t>Elite Shield Guard (精英-冰甲卫士)</t>
   </si>
   <si>
-    <t>厚实半圆形</t>
-  </si>
-  <si>
     <t>警惕且坚毅眼</t>
   </si>
   <si>
@@ -933,9 +930,6 @@
   </si>
   <si>
     <t>Elite Aura (精英凛冬散布者)</t>
-  </si>
-  <si>
-    <t>巨大菱形</t>
   </si>
   <si>
     <t>高傲的蔑视眼/闭目</t>
@@ -1962,7 +1956,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2030,6 +2024,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2085,6 +2082,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2414,7 +2417,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="103" customHeight="1" spans="1:4">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2791,10 +2794,10 @@
       </c>
     </row>
     <row r="8" ht="28.95" customHeight="1" spans="1:3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>79</v>
       </c>
       <c r="C8" s="16"/>
@@ -2803,7 +2806,7 @@
       <c r="A9" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="25" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -2814,7 +2817,7 @@
       <c r="A10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C10" s="16" t="s">
@@ -2825,7 +2828,7 @@
       <c r="A11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="25" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="16"/>
@@ -2861,39 +2864,39 @@
     </row>
     <row r="20" ht="15.15" customHeight="1"/>
     <row r="21" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="27" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="22" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="19" t="s">
@@ -2901,19 +2904,19 @@
       </c>
     </row>
     <row r="23" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="31" t="s">
         <v>111</v>
       </c>
       <c r="F23" s="19" t="s">
@@ -2921,19 +2924,19 @@
       </c>
     </row>
     <row r="24" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="31" t="s">
         <v>117</v>
       </c>
       <c r="F24" s="19" t="s">
@@ -2941,19 +2944,19 @@
       </c>
     </row>
     <row r="25" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="29" t="s">
         <v>123</v>
       </c>
       <c r="F25" s="19" t="s">
@@ -2961,39 +2964,39 @@
       </c>
     </row>
     <row r="26" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="35" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="27" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="31" t="s">
         <v>135</v>
       </c>
       <c r="F27" s="19" t="s">
@@ -3001,19 +3004,19 @@
       </c>
     </row>
     <row r="28" ht="15.15" customHeight="1" spans="1:6">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="37" t="s">
         <v>139</v>
       </c>
       <c r="F28" s="19" t="s">
@@ -3021,19 +3024,19 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="37" t="s">
         <v>143</v>
       </c>
       <c r="F29" s="19" t="s">
@@ -3044,10 +3047,10 @@
       <c r="A30" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="37" t="s">
         <v>147</v>
       </c>
       <c r="D30" s="21" t="s">
@@ -3056,7 +3059,7 @@
       <c r="E30" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="36" t="s">
+      <c r="F30" s="37" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3064,16 +3067,16 @@
       <c r="A31" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F31" s="19" t="s">
@@ -3087,10 +3090,10 @@
       <c r="B32" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="37" t="s">
         <v>154</v>
       </c>
       <c r="E32" s="20" t="s">
@@ -3104,18 +3107,18 @@
       <c r="A33" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B33" s="37"/>
+      <c r="B33" s="38"/>
       <c r="C33" s="21"/>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="30"/>
+      <c r="E33" s="31"/>
     </row>
     <row r="34" s="21" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="29" t="s">
         <v>114</v>
       </c>
       <c r="C34" s="21" t="s">
@@ -3124,7 +3127,7 @@
       <c r="D34" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="31" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3132,57 +3135,57 @@
       <c r="A35" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="E35" s="36" t="s">
+      <c r="E35" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="37" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="36" s="22" customFormat="1" spans="1:6">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="E36" s="39" t="s">
+      <c r="E36" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="39"/>
+      <c r="F36" s="40"/>
     </row>
     <row r="37" s="22" customFormat="1" spans="1:6">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="E37" s="39" t="s">
+      <c r="E37" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="F37" s="39"/>
+      <c r="F37" s="40"/>
     </row>
     <row r="38" ht="43.2" spans="1:6">
       <c r="A38" s="19" t="s">
@@ -3191,16 +3194,16 @@
       <c r="B38" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="39" t="s">
         <v>158</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F38" s="36" t="s">
+      <c r="F38" s="37" t="s">
         <v>181</v>
       </c>
     </row>
@@ -3208,39 +3211,39 @@
       <c r="A39" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="B39" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="37" t="s">
         <v>185</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="37" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="40" s="22" customFormat="1" spans="1:6">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="40" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3248,7 +3251,7 @@
       <c r="A41" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="37" t="s">
         <v>195</v>
       </c>
       <c r="C41" s="21" t="s">
@@ -3260,22 +3263,22 @@
       <c r="E41" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F41" s="36"/>
+      <c r="F41" s="37"/>
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="31" t="s">
         <v>105</v>
       </c>
       <c r="F42" s="19" t="s">
@@ -3286,19 +3289,19 @@
       <c r="A43" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="37" t="s">
         <v>202</v>
       </c>
       <c r="E43" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="37" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3306,13 +3309,13 @@
       <c r="A44" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="37" t="s">
         <v>206</v>
       </c>
       <c r="E44" s="19" t="s">
@@ -3326,13 +3329,13 @@
       <c r="A45" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C45" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="37" t="s">
         <v>212</v>
       </c>
       <c r="E45" s="19" t="s">
@@ -3342,119 +3345,119 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" s="22" customFormat="1" spans="1:6">
-      <c r="A46" s="34" t="s">
+    <row r="46" s="23" customFormat="1" spans="1:6">
+      <c r="A46" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="44" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="47" s="22" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="39" t="s">
+      <c r="D47" s="40" t="s">
         <v>224</v>
       </c>
       <c r="E47" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="F47" s="39"/>
+      <c r="F47" s="40"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="B48" s="36" t="s">
+      <c r="B48" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="D48" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="E48" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F48" s="37" t="s">
         <v>230</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B49" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C49" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="D49" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="E49" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="F49" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="E49" s="19" t="s">
+    </row>
+    <row r="50" s="22" customFormat="1" spans="1:6">
+      <c r="A50" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="F49" s="36" t="s">
+      <c r="B50" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="35" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="50" s="22" customFormat="1" spans="1:6">
-      <c r="A50" s="34" t="s">
+      <c r="D50" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="B50" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="C50" s="34" t="s">
+      <c r="E50" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="D50" s="39" t="s">
+      <c r="F50" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="E50" s="34" t="s">
+    </row>
+    <row r="51" ht="28.8" spans="1:6">
+      <c r="A51" s="37" t="s">
         <v>241</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="B51" s="1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="51" ht="28.8" spans="1:6">
-      <c r="A51" s="36" t="s">
+      <c r="C51" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="D51" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="E51" s="21" t="s">
         <v>245</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3485,125 +3488,125 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4" ht="15.15" customHeight="1" spans="1:3">
       <c r="A4" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A5" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="6" ht="15.15" customHeight="1" spans="1:3">
       <c r="A6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="15.15" customHeight="1" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" ht="15.15" customHeight="1" spans="1:3">
       <c r="A8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="9" ht="15.15" customHeight="1" spans="1:3">
       <c r="A9" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="10" ht="15.15" customHeight="1" spans="1:3">
       <c r="A10" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="11" ht="15.15" customHeight="1" spans="1:3">
       <c r="A11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -3624,30 +3627,30 @@
     </row>
     <row r="21" ht="43.95" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="22" ht="29.55" customHeight="1" spans="1:5">
       <c r="A22" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="27" ht="15.15" customHeight="1"/>
@@ -3667,110 +3670,110 @@
     </row>
     <row r="29" ht="58.35" customHeight="1" spans="1:5">
       <c r="A29" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="D29" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="30" ht="43.95" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" t="s">
         <v>295</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="E30" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="31" ht="58.35" customHeight="1" spans="1:5">
       <c r="A31" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="E31" t="s">
         <v>300</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="E31" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="32" ht="43.95" customHeight="1" spans="1:5">
       <c r="A32" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="E32" t="s">
         <v>305</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="E32" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="33" ht="29.55" customHeight="1" spans="1:4">
       <c r="A33" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="34" ht="43.2" customHeight="1" spans="1:4">
       <c r="A34" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="D34" s="18" t="s">
         <v>312</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="35" ht="87" customHeight="1" spans="1:4">
       <c r="A35" s="19"/>
       <c r="B35" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D35" s="19"/>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
